--- a/summary.xlsx
+++ b/summary.xlsx
@@ -536,7 +536,7 @@
   <dimension ref="A1:AN103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" min="2" max="3"/>
+    <col hidden="1" width="13" customWidth="1" min="2" max="3"/>
     <col width="9.140625" customWidth="1" style="1" min="18" max="101"/>
   </cols>
   <sheetData>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA VeraRubin NVL72 (72x VR-288GB_aarch64)</t>
+          <t>NVIDIA Vera Rubin NVL72 (72x VR-288GB_aarch64)</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA VeraRubin</t>
+          <t>NVIDIA Vera Rubin</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA VeraRubin NVL72, 2300W TGP Per GPU</t>
+          <t>NVIDIA Vera Rubin NVL72, 2300W TGP Per GPU</t>
         </is>
       </c>
       <c r="P101" s="2">
@@ -9381,7 +9381,7 @@
   <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" min="2" max="3"/>
+    <col hidden="1" width="13" customWidth="1" min="2" max="3"/>
     <col width="9.140625" customWidth="1" style="1" min="18" max="101"/>
   </cols>
   <sheetData>
@@ -10395,7 +10395,7 @@
   <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" min="2" max="3"/>
+    <col hidden="1" width="13" customWidth="1" min="2" max="3"/>
     <col width="9.140625" customWidth="1" style="1" min="18" max="101"/>
   </cols>
   <sheetData>
@@ -11526,7 +11526,7 @@
   <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" min="2" max="3"/>
+    <col hidden="1" width="13" customWidth="1" min="2" max="3"/>
     <col width="9.140625" customWidth="1" style="1" min="18" max="101"/>
   </cols>
   <sheetData>
